--- a/Result/profitability/3628.xlsx
+++ b/Result/profitability/3628.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM72"/>
+  <dimension ref="A1:AM73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,7 +672,7 @@
         <v>0.89375</v>
       </c>
       <c r="N2" t="n">
-        <v>27.45</v>
+        <v>27.75125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>1.065</v>
+        <v>0.9837500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>27.13375</v>
+        <v>27.745</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0075</v>
+        <v>1.0625</v>
       </c>
       <c r="N4" t="n">
-        <v>26.04375</v>
+        <v>26.5975</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.055</v>
       </c>
       <c r="N5" t="n">
-        <v>26.975</v>
+        <v>26.74125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.63</v>
       </c>
       <c r="M6" t="n">
-        <v>1.055</v>
+        <v>0.865</v>
       </c>
       <c r="N6" t="n">
-        <v>22.1175</v>
+        <v>22.06125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0.9550000000000001</v>
+        <v>0.9075000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>24.505</v>
+        <v>24.7425</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9837500000000001</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
-        <v>25.095</v>
+        <v>25.51625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9572,6 +9572,133 @@
       </c>
       <c r="AM72" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>3628</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>945</v>
+      </c>
+      <c r="D73" t="n">
+        <v>656</v>
+      </c>
+      <c r="E73" t="n">
+        <v>289</v>
+      </c>
+      <c r="F73" t="n">
+        <v>30.56</v>
+      </c>
+      <c r="G73" t="n">
+        <v>74</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>7.80%</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>-5</v>
+      </c>
+      <c r="J73" t="n">
+        <v>69</v>
+      </c>
+      <c r="K73" t="n">
+        <v>28</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.8625</v>
+      </c>
+      <c r="N73" t="n">
+        <v>28.725</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>0</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W73" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X73" t="n">
+        <v>0.8529411764705881</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>3.369999999999997</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.1239426259654284</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>-0.05970149253731349</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>-1.870000000000001</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>-0.05766265803268578</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK73" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
